--- a/out/LSTM-Mamba1_repeat_5_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.778954327415217</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.378954327415217</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002356597056937171</v>
+        <v>-6.75351114863297e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.716808359578216</v>
+        <v>0.7785800168151985</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.437816414581343</v>
+        <v>1.558363729382479</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4073975325912402</v>
+        <v>0.1167515465921939</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.532156789670084</v>
+        <v>1.012241738182021</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5093794743235076</v>
+        <v>0.1459774784774187</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.143582903295176</v>
+        <v>1.18746364413097</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7301930607606847</v>
+        <v>0.209257860438623</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.09487701587595</v>
+        <v>1.460084593687064</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7811619385294082</v>
+        <v>0.2238644609173098</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.927062274056149</v>
+        <v>1.698571628299907</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8278742043601506</v>
+        <v>0.237251944347076</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.801707854762856</v>
+        <v>1.949227299831098</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.37360356511927</v>
+        <v>0.1070667240257002</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.720354153202081</v>
+        <v>1.925912980847788</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1804340889883025</v>
+        <v>0.05170897721724928</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.707324477044236</v>
+        <v>1.922178923545358</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08597085864259292</v>
+        <v>0.02463717527422079</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.698690042381052</v>
+        <v>1.919704459501471</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02547292892220793</v>
+        <v>0.007297419349351257</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.663572239278294</v>
+        <v>1.909637419604475</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01684939258332941</v>
+        <v>0.004825271689484421</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.671784795059819</v>
+        <v>1.911987494252265</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008621334514552999</v>
+        <v>0.002466695254996821</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.672167916009575</v>
+        <v>1.912093724905556</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004407200148488257</v>
+        <v>0.001259367644650069</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.672356857510089</v>
+        <v>1.912144317334213</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001654091738465106</v>
+        <v>0.0004703237279909154</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.671253490701427</v>
+        <v>1.911824389174857</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008992065510754283</v>
+        <v>0.0002540518768592011</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.671396887831452</v>
+        <v>1.911861972613917</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000430512012905964</v>
+        <v>0.0001197726022376576</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.671358133555464</v>
+        <v>1.911847271824636</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000264603702177201</v>
+        <v>7.273245427736819e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.671456625296971</v>
+        <v>1.911872110684413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001360235745755069</v>
+        <v>3.514539714193261e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.671463912102028</v>
+        <v>1.911870653856644</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.293833289339209e-05</v>
+        <v>1.498186261570356e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.671454676606754</v>
+        <v>1.911864417038152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.849097684393219e-05</v>
+        <v>7.791463777627117e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.671468970709035</v>
+        <v>1.911865009306555</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.671459968131211</v>
+        <v>1.911858865510579</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.671452501554217</v>
+        <v>1.911853180976551</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.671448246376046</v>
+        <v>1.911848429701337</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.671442524097016</v>
+        <v>1.911843140553775</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.671437454741647</v>
+        <v>1.911843117819474</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.671433089767679</v>
+        <v>1.91184343609969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.671434181014136</v>
+        <v>1.911844527346148</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.671433491407</v>
+        <v>1.911843837739012</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.671433521719401</v>
+        <v>1.911843868051413</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.671433332266892</v>
+        <v>1.911843678598903</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.671433385313595</v>
+        <v>1.911843731645606</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.671433438360297</v>
+        <v>1.911843784692309</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.671433400469795</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.671433271642088</v>
+        <v>1.9118436179741</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.671433127658181</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.671432968518073</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.671433021564775</v>
+        <v>1.911843367896787</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.671432968518073</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.671432968518073</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.671432786643663</v>
+        <v>1.911843132975675</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.671432953361871</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.671433150392482</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.671432991252374</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.671433029142875</v>
+        <v>1.911843375474887</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.671433226173486</v>
+        <v>1.911843572505498</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.671433203439184</v>
+        <v>1.911843549771197</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.671433051877177</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.671432976096173</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.671433074611478</v>
+        <v>1.91184342094349</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.671433082189578</v>
+        <v>1.91184342852159</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.671433347423092</v>
+        <v>1.911843693755104</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.671433051877177</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.671433294376389</v>
+        <v>1.911843640708401</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.671433377735494</v>
+        <v>1.911843724067505</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.671433211017286</v>
+        <v>1.911843557349297</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.671433400469795</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.671433051877177</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.671432847268466</v>
+        <v>1.911843193600478</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.671432960939971</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.671432976096173</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.671432741175061</v>
+        <v>1.911843087507072</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.671432801799863</v>
+        <v>1.911843148131875</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.671432672972156</v>
+        <v>1.911843019304169</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.671432809377965</v>
+        <v>1.911843155709976</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.671432983674273</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.671433127658181</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.671432960939971</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.671432953361871</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.671432665394057</v>
+        <v>1.911843011726068</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.671432680550257</v>
+        <v>1.911843026882269</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.671432907893269</v>
+        <v>1.911843254225281</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.671432892737069</v>
+        <v>1.91184323906908</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.671432998830474</v>
+        <v>1.911843345162486</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.67143272601886</v>
+        <v>1.911843072350872</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.671432824534165</v>
+        <v>1.911843170866177</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.671432976096173</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.671432991252374</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.671432968518073</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.671433051877177</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.671433150392482</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.671432983674273</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.671432968518073</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.671432938205671</v>
+        <v>1.911843284537683</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.67143292304947</v>
+        <v>1.911843269381482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.671432960939971</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.671432976096173</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.671432968518073</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002356597056937171</v>
+        <v>-0.0002056608579123858</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.716808359578216</v>
+        <v>2.370965874459884</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.778954327415217</v>
+        <v>0.6948861808537512</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.437816414581343</v>
+        <v>4.74559698583189</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4073975325912402</v>
+        <v>0.3555369092220213</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353367</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.532156789670084</v>
+        <v>3.082522661392779</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5093794743235076</v>
+        <v>0.4445368207564149</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.143582903295176</v>
+        <v>3.616115923627147</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7301930607606847</v>
+        <v>0.6372415870570858</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.09487701587595</v>
+        <v>4.446313035371153</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7811619385294082</v>
+        <v>0.681721925414604</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.927062274056149</v>
+        <v>5.172563507383049</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8278742043601506</v>
+        <v>0.7224885712680423</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.801707854762856</v>
+        <v>5.935869614328485</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.37360356511927</v>
+        <v>0.3260449889484451</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.720354153202081</v>
+        <v>5.864871968560571</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1804340889883025</v>
+        <v>0.157465470435821</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.707324477044236</v>
+        <v>5.853500923890876</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08597085864259292</v>
+        <v>0.07502699572163948</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.698690042381052</v>
+        <v>5.84596562220573</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02547292892220793</v>
+        <v>0.02223033867729131</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.663572239278294</v>
+        <v>5.815318158815836</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01684939258332941</v>
+        <v>0.01470401838656529</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.671784795059819</v>
+        <v>5.822484771205983</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008621334514552999</v>
+        <v>0.007523240603495494</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.672167916009575</v>
+        <v>5.822818486089817</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004407200148488257</v>
+        <v>0.003845482675785441</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.672356857510089</v>
+        <v>5.822982739780258</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001654091738465106</v>
+        <v>0.001442920846571053</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.671253490701427</v>
+        <v>5.822019174221421</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008992065510754283</v>
+        <v>0.0007837057142592239</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.671396887831452</v>
+        <v>5.822143683716574</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000430512012905964</v>
+        <v>0.000374880916366881</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.671358133555464</v>
+        <v>5.822109210805775</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000264603702177201</v>
+        <v>0.0002301652730669746</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.671456625296971</v>
+        <v>5.822194672251789</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001360235745755069</v>
+        <v>0.0001185242988982542</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.671463912102028</v>
+        <v>5.822200434416802</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.293833289339209e-05</v>
+        <v>5.494558784711067e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.671454676606754</v>
+        <v>5.822191723961327</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.849097684393219e-05</v>
+        <v>3.337439133288135e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.671468970709035</v>
+        <v>5.822203500766531</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>1.248416916455026e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.671459968131211</v>
+        <v>5.822195069378603</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>2.205584102398162e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.671452501554217</v>
+        <v>5.822188014524023</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.671448246376046</v>
+        <v>5.822183675986749</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.671442524097016</v>
+        <v>5.822178097691626</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.671437454741647</v>
+        <v>5.822173051070558</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.671433089767679</v>
+        <v>5.822173369350774</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.671434181014136</v>
+        <v>5.822174460597231</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.671433491407</v>
+        <v>5.822173770990095</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.671433521719401</v>
+        <v>5.822173801302498</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.671433332266892</v>
+        <v>5.822173611849987</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.671433385313595</v>
+        <v>5.82217366489669</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.671433438360297</v>
+        <v>5.822173717943393</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.671433400469795</v>
+        <v>5.822173680052891</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.671433271642088</v>
+        <v>5.822173551225183</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.671433127658181</v>
+        <v>5.822173407241277</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.671432968518073</v>
+        <v>5.822173248101168</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.671433021564775</v>
+        <v>5.82217330114787</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.671432968518073</v>
+        <v>5.822173248101168</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.671432968518073</v>
+        <v>5.822173248101168</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.671432786643663</v>
+        <v>5.822173066226759</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.671432953361871</v>
+        <v>5.822173232944968</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.671433150392482</v>
+        <v>5.822173429975578</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.671432991252374</v>
+        <v>5.82217327083547</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.671433029142875</v>
+        <v>5.82217330872597</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.671433226173486</v>
+        <v>5.822173505756581</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.671433203439184</v>
+        <v>5.82217348302228</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.671433051877177</v>
+        <v>5.822173331460272</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.671432976096173</v>
+        <v>5.822173255679268</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.671433074611478</v>
+        <v>5.822173354194574</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.671433082189578</v>
+        <v>5.822173361772674</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.671433347423092</v>
+        <v>5.822173627006188</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.671433051877177</v>
+        <v>5.822173331460272</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.671433294376389</v>
+        <v>5.822173573959485</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.671433377735494</v>
+        <v>5.822173657318589</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.671433211017286</v>
+        <v>5.822173490600381</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.671433400469795</v>
+        <v>5.822173680052891</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.671433051877177</v>
+        <v>5.822173331460272</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.671432847268466</v>
+        <v>5.822173126851562</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.671432960939971</v>
+        <v>5.822173240523068</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.671432976096173</v>
+        <v>5.822173255679268</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.671432741175061</v>
+        <v>5.822173020758156</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.671432801799863</v>
+        <v>5.822173081382959</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.671432672972156</v>
+        <v>5.822172952555253</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.671432809377965</v>
+        <v>5.82217308896106</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.671432983674273</v>
+        <v>5.822173263257368</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.671433127658181</v>
+        <v>5.822173407241277</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.671432960939971</v>
+        <v>5.822173240523068</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.671432953361871</v>
+        <v>5.822173232944968</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.671432665394057</v>
+        <v>5.822172944977152</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.671432680550257</v>
+        <v>5.822172960133353</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.671432907893269</v>
+        <v>5.822173187476364</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.671432892737069</v>
+        <v>5.822173172320164</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.671432998830474</v>
+        <v>5.82217327841357</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.67143272601886</v>
+        <v>5.822173005601956</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.671432824534165</v>
+        <v>5.82217310411726</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.671432976096173</v>
+        <v>5.822173255679268</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.671432991252374</v>
+        <v>5.82217327083547</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.671432968518073</v>
+        <v>5.822173248101168</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.671433051877177</v>
+        <v>5.822173331460272</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.671433150392482</v>
+        <v>5.822173429975578</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.671432983674273</v>
+        <v>5.822173263257368</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.671432968518073</v>
+        <v>5.822173248101168</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.671432938205671</v>
+        <v>5.822173217788766</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.67143292304947</v>
+        <v>5.822173202632566</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.671432960939971</v>
+        <v>5.822173240523068</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.671432976096173</v>
+        <v>5.822173255679268</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.671432968518073</v>
+        <v>5.822173248101168</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01710628345608711</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.009337903931736946</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005014192312955856</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.002901310101151466</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001685561612248421</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0009673405438661575</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0005569588392972946</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0004070773720741272</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0004128552973270416</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0004657600075006485</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.385568681656149</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0005215220153331757</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.385568681656149</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0005635712295770645</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.385568681656149</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0006847605109214783</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.385568681656149</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0007391590625047684</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.385568681656149</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0008145961910486221</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0008406545966863632</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0009169187396764755</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0009580980986356735</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001062273979187012</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.00120757520198822</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001374160870909691</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001590203493833542</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0014523696154356</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001212149858474731</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001000260934233665</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0008503831923007965</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0007434897124767303</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0008335709571838379</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0008406955748796463</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.000775730237364769</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0006902702152729034</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0005951393395662308</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0005838107317686081</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0006130505353212357</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.385568681656149</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0008201021701097488</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.385568681656149</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001480920240283012</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.385568681656149</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001283137127757072</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.385568681656149</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0008126664906740189</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.385568681656149</v>
+        <v>0.3</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002056608579123858</v>
+        <v>-0.0001228774378865491</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.370965874459884</v>
+        <v>1.416595380491756</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0002513695508241653</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6948861808537512</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.74559698583189</v>
+        <v>2.83538056179056</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3555369092220213</v>
+        <v>0.2124247964188713</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0002210382372140884</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.004203680051353367</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.082522661392779</v>
+        <v>1.841733508283243</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4445368207564149</v>
+        <v>0.2656000573417474</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0006171595305204391</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.616115923627147</v>
+        <v>2.160542674663371</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6372415870570858</v>
+        <v>0.3807364226172426</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0005819108337163925</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.446313035371153</v>
+        <v>2.656565564610953</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.681721925414604</v>
+        <v>0.4073129040715802</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0004840288311243057</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.172563507383049</v>
+        <v>3.090483011834572</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7224885712680423</v>
+        <v>0.43166884285106</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0006229598075151443</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.935869614328485</v>
+        <v>3.546540091439789</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3260449889484451</v>
+        <v>0.1948047861298235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0009630229324102402</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.864871968560571</v>
+        <v>3.504120629035562</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.157465470435821</v>
+        <v>0.09408180784769798</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.002280822023749352</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.853500923890876</v>
+        <v>3.497326705029995</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07502699572163948</v>
+        <v>0.04482718044570647</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003022836521267891</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.84596562220573</v>
+        <v>3.49282454407493</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02223033867729131</v>
+        <v>0.01328104356247639</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003640754148364067</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.815318158815836</v>
+        <v>3.474512638650395</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01470401838656529</v>
+        <v>0.00878273010652071</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00381946749985218</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.822484771205983</v>
+        <v>3.478792469079985</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007523240603495494</v>
+        <v>0.004492658841795569</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003978302702307701</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.822818486089817</v>
+        <v>3.478989853039486</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003845482675785441</v>
+        <v>0.002296229646234122</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003847779706120491</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.822982739780258</v>
+        <v>3.479085993422685</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001442920846571053</v>
+        <v>0.0008601194603401532</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003622880205512047</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.822019174221421</v>
+        <v>3.478508259270176</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007837057142592239</v>
+        <v>0.000466078413014662</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003448089584708214</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.822143683716574</v>
+        <v>3.478580640211442</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000374880916366881</v>
+        <v>0.0002222927658596819</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003245377913117409</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.822109210805775</v>
+        <v>3.478558023928718</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002301652730669746</v>
+        <v>0.0001357055817932108</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003066910430788994</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.822194672251789</v>
+        <v>3.478607036041986</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001185242988982542</v>
+        <v>6.808521018146706e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003161890432238579</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.822200434416802</v>
+        <v>3.478608449124887</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.494558784711067e-05</v>
+        <v>3.09673527082664e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002300379797816277</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.822191723961327</v>
+        <v>3.478601222851602</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.337439133288135e-05</v>
+        <v>1.802463479972881e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002430642023682594</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.822203500766531</v>
+        <v>3.478606288934726</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003187382593750954</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.822195069378603</v>
+        <v>3.47859923010197</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003664372488856316</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.822188014524023</v>
+        <v>3.478592997439721</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.00386044941842556</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.822183675986749</v>
+        <v>3.478588411530188</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003828456625342369</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.822178097691626</v>
+        <v>3.47858297839872</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003474446013569832</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.822173051070558</v>
+        <v>3.478577931777652</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002708809450268745</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.822173369350774</v>
+        <v>3.478578250057869</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001973440870642662</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.822174460597231</v>
+        <v>3.478579341304326</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002681339159607887</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.822173770990095</v>
+        <v>3.47857865169719</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.004036566242575645</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.822173801302498</v>
+        <v>3.478578682009592</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.005060391500592232</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.822173611849987</v>
+        <v>3.478578492557082</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.005580617114901543</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.82217366489669</v>
+        <v>3.478578545603785</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005860725417733192</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.822173717943393</v>
+        <v>3.478578598650487</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.00583893246948719</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.822173680052891</v>
+        <v>3.478578560759985</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.005567217245697975</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.822173551225183</v>
+        <v>3.478578431932278</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.005201591178774834</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.822173407241277</v>
+        <v>3.478578287948371</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.004803167656064034</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.822173248101168</v>
+        <v>3.478578128808263</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004447506740689278</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.82217330114787</v>
+        <v>3.478578181854965</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004242056980729103</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.822173248101168</v>
+        <v>3.478578128808263</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.00401824526488781</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.822173248101168</v>
+        <v>3.478578128808263</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003641178831458092</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.822173066226759</v>
+        <v>3.478577946933854</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003362992778420448</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.822173232944968</v>
+        <v>3.478578113652062</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003455521538853645</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.822173429975578</v>
+        <v>3.478578310682672</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003600964322686195</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.82217327083547</v>
+        <v>3.478578151542564</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003496078774333</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.82217330872597</v>
+        <v>3.478578189433065</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003400085493922234</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.822173505756581</v>
+        <v>3.478578386463675</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003615817055106163</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.82217348302228</v>
+        <v>3.478578363729374</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003845157101750374</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.822173331460272</v>
+        <v>3.478578212167367</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003883650526404381</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.822173255679268</v>
+        <v>3.478578136386363</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003825491294264793</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.822173354194574</v>
+        <v>3.478578234901669</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003620540723204613</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.822173361772674</v>
+        <v>3.478578242479768</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003662766888737679</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.822173627006188</v>
+        <v>3.478578507713283</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003764407709240913</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.822173331460272</v>
+        <v>3.478578212167367</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003731837496161461</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.822173573959485</v>
+        <v>3.478578454666579</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003978928551077843</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.822173657318589</v>
+        <v>3.478578538025684</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003717957064509392</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.822173490600381</v>
+        <v>3.478578371307476</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003981204703450203</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.822173680052891</v>
+        <v>3.478578560759985</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004310401156544685</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.822173331460272</v>
+        <v>3.478578212167367</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004494568333029747</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.822173126851562</v>
+        <v>3.478578007558656</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.004414288327097893</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.822173240523068</v>
+        <v>3.478578121230162</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.004192983731627464</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.822173255679268</v>
+        <v>3.478578136386363</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003890899941325188</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.822173020758156</v>
+        <v>3.478577901465251</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003706743940711021</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.822173081382959</v>
+        <v>3.478577962090053</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00347280316054821</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.822172952555253</v>
+        <v>3.478577833262347</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002986887469887733</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.82217308896106</v>
+        <v>3.478577969668155</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002972526475787163</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.822173263257368</v>
+        <v>3.478578143964463</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003175375983119011</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.822173407241277</v>
+        <v>3.478578287948371</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003270598128437996</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.822173240523068</v>
+        <v>3.478578121230162</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003397310152649879</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.822173232944968</v>
+        <v>3.478578113652062</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003428259864449501</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.822172944977152</v>
+        <v>3.478577825684247</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003255007788538933</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.822172960133353</v>
+        <v>3.478577840840448</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003130903467535973</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.822173187476364</v>
+        <v>3.478578068183459</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002951560541987419</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.822173172320164</v>
+        <v>3.478578053027258</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003063878044486046</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.82217327841357</v>
+        <v>3.478578159120664</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0030862707644701</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.822173005601956</v>
+        <v>3.47857788630905</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002986745908856392</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.82217310411726</v>
+        <v>3.478577984824355</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002954533323645592</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.822173255679268</v>
+        <v>3.478578136386363</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00298457033932209</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.82217327083547</v>
+        <v>3.478578151542564</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003011947497725487</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.822173248101168</v>
+        <v>3.478578128808263</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003025466576218605</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.822173331460272</v>
+        <v>3.478578212167367</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003193071112036705</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.822173429975578</v>
+        <v>3.478578310682672</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003343066200613976</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.822173263257368</v>
+        <v>3.478578143964463</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003365045413374901</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.822173248101168</v>
+        <v>3.478578128808263</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003324339166283607</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.822173217788766</v>
+        <v>3.478578098495861</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003253372386097908</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.822173202632566</v>
+        <v>3.47857808333966</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003227485343813896</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.822173240523068</v>
+        <v>3.478578121230162</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003183377906680107</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.7900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.822173255679268</v>
+        <v>3.478578136386363</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003130180761218071</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6864788207510445</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.822173248101168</v>
+        <v>3.478578128808263</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.01710628345608711</v>
+        <v>0.0171063095331192</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.009337903931736946</v>
+        <v>0.009337909519672394</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.005014192312955856</v>
+        <v>0.005014229565858841</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.002901310101151466</v>
+        <v>0.002901362255215645</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.001685561612248421</v>
+        <v>0.001685589551925659</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0005569588392972946</v>
+        <v>0.0005569569766521454</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.0004070773720741272</v>
+        <v>0.0004070606082677841</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0004128552973270416</v>
+        <v>0.0004128310829401016</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0004657600075006485</v>
+        <v>0.0004657469689846039</v>
       </c>
       <c r="JB11" t="n">
         <v>0.4399999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.0005215220153331757</v>
+        <v>0.0005215425044298172</v>
       </c>
       <c r="JB12" t="n">
         <v>0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0005635712295770645</v>
+        <v>0.0005635786801576614</v>
       </c>
       <c r="JB13" t="n">
         <v>0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0006847605109214783</v>
+        <v>0.0006847530603408813</v>
       </c>
       <c r="JB14" t="n">
         <v>0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0007391590625047684</v>
+        <v>0.0007391031831502914</v>
       </c>
       <c r="JB15" t="n">
         <v>0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0008145961910486221</v>
+        <v>0.000814530998468399</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0008406545966863632</v>
+        <v>0.0008406620472669601</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0009169187396764755</v>
+        <v>0.0009169522672891617</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0009580980986356735</v>
+        <v>0.0009581036865711212</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001062273979187012</v>
+        <v>0.001062225550413132</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.00120757520198822</v>
+        <v>0.001207591965794563</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001374160870909691</v>
+        <v>0.001374144107103348</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001590203493833542</v>
+        <v>0.001590173691511154</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0014523696154356</v>
+        <v>0.00145232304930687</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001212149858474731</v>
+        <v>0.001212097704410553</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.001000260934233665</v>
+        <v>0.001000214368104935</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0008503831923007965</v>
+        <v>0.000850386917591095</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0007434897124767303</v>
+        <v>0.0007435288280248642</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0008335709571838379</v>
+        <v>0.0008336249738931656</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0008406955748796463</v>
+        <v>0.0008407197892665863</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.000775730237364769</v>
+        <v>0.0007757283747196198</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0006902702152729034</v>
+        <v>0.0006902460008859634</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0005951393395662308</v>
+        <v>0.0005951337516307831</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0005838107317686081</v>
+        <v>0.0005837827920913696</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.2599999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.0006130505353212357</v>
+        <v>0.0006130300462245941</v>
       </c>
       <c r="JB35" t="n">
         <v>0.02000000000000007</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0008201021701097488</v>
+        <v>0.0008200667798519135</v>
       </c>
       <c r="JB36" t="n">
         <v>0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.001480920240283012</v>
+        <v>0.001480905339121819</v>
       </c>
       <c r="JB37" t="n">
         <v>0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001283137127757072</v>
+        <v>0.001283112913370132</v>
       </c>
       <c r="JB38" t="n">
         <v>0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.0008126664906740189</v>
+        <v>0.0008126217871904373</v>
       </c>
       <c r="JB39" t="n">
         <v>0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.0002513695508241653</v>
+        <v>0.00025133416056633</v>
       </c>
       <c r="JB40" t="n">
         <v>0.02000000000000007</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0002210382372140884</v>
+        <v>-0.0002210792154073715</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0006171595305204391</v>
+        <v>-0.0006172172725200653</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0005819108337163925</v>
+        <v>-0.0005819685757160187</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0004840288311243057</v>
+        <v>-0.000484079122543335</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0006229598075151443</v>
+        <v>-0.0006230361759662628</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0009630229324102402</v>
+        <v>-0.0009632222354412079</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.002280822023749352</v>
+        <v>-0.002280991524457932</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.003022836521267891</v>
+        <v>-0.003022901713848114</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.003640754148364067</v>
+        <v>-0.003640856593847275</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.00381946749985218</v>
+        <v>-0.003819543868303299</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.003978302702307701</v>
+        <v>-0.003978382796049118</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.003847779706120491</v>
+        <v>-0.003847856074571609</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.003622880205512047</v>
+        <v>-0.003622882068157196</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.003448089584708214</v>
+        <v>-0.00344814732670784</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.003245377913117409</v>
+        <v>-0.003245409578084946</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.003066910430788994</v>
+        <v>-0.003066942095756531</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003161890432238579</v>
+        <v>-0.003161966800689697</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.002300379797816277</v>
+        <v>-0.00230049341917038</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.002430642023682594</v>
+        <v>-0.002430737018585205</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003187382593750954</v>
+        <v>-0.003187492489814758</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003664372488856316</v>
+        <v>-0.003664460033178329</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.00386044941842556</v>
+        <v>-0.003860548138618469</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.003828456625342369</v>
+        <v>-0.003828540444374084</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.003474446013569832</v>
+        <v>-0.003474541008472443</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.002708809450268745</v>
+        <v>-0.002708800137042999</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.001973440870642662</v>
+        <v>-0.001973506063222885</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.1199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002681339159607887</v>
+        <v>-0.002681449055671692</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.004036566242575645</v>
+        <v>-0.004037074744701385</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.005060391500592232</v>
+        <v>-0.005060579627752304</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.3999999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.005580617114901543</v>
+        <v>-0.00558074563741684</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.005860725417733192</v>
+        <v>-0.005860935896635056</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.00583893246948719</v>
+        <v>-0.005839038640260696</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.005567217245697975</v>
+        <v>-0.005567248910665512</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.005201591178774834</v>
+        <v>-0.005201656371355057</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.004803167656064034</v>
+        <v>-0.004803221672773361</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.004447506740689278</v>
+        <v>-0.004447612911462784</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.004242056980729103</v>
+        <v>-0.004242081195116043</v>
       </c>
       <c r="JB77" t="n">
         <v>0.02000000000000007</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.00401824526488781</v>
+        <v>-0.004018224775791168</v>
       </c>
       <c r="JB78" t="n">
         <v>0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.003641178831458092</v>
+        <v>-0.003641121089458466</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003362992778420448</v>
+        <v>-0.003362987190485001</v>
       </c>
       <c r="JB80" t="n">
         <v>0.8599999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.003455521538853645</v>
+        <v>-0.003455519676208496</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.003600964322686195</v>
+        <v>-0.003601007163524628</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003496078774333</v>
+        <v>-0.003496132791042328</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.003400085493922234</v>
+        <v>-0.003400128334760666</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.003615817055106163</v>
+        <v>-0.003615856170654297</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003845157101750374</v>
+        <v>-0.003845207393169403</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003883650526404381</v>
+        <v>-0.003883760422468185</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003825491294264793</v>
+        <v>-0.00382554903626442</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.003620540723204613</v>
+        <v>-0.003620568662881851</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.003662766888737679</v>
+        <v>-0.003662757575511932</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.003764407709240913</v>
+        <v>-0.003764413297176361</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.02000000000000007</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003731837496161461</v>
+        <v>-0.003731884062290192</v>
       </c>
       <c r="JB92" t="n">
         <v>0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003978928551077843</v>
+        <v>-0.003978893160820007</v>
       </c>
       <c r="JB93" t="n">
         <v>0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003717957064509392</v>
+        <v>-0.003717955201864243</v>
       </c>
       <c r="JB94" t="n">
         <v>0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003981204703450203</v>
+        <v>-0.00398123636841774</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.004310401156544685</v>
+        <v>-0.004310458898544312</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.004494568333029747</v>
+        <v>-0.004494614899158478</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.004414288327097893</v>
+        <v>-0.004414331167936325</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.004192983731627464</v>
+        <v>-0.004192989319562912</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.003890899941325188</v>
+        <v>-0.003890920430421829</v>
       </c>
       <c r="JB100" t="n">
         <v>0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.003706743940711021</v>
+        <v>-0.003706730902194977</v>
       </c>
       <c r="JB101" t="n">
         <v>0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.00347280316054821</v>
+        <v>-0.003472786396741867</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.002986887469887733</v>
+        <v>-0.002986863255500793</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002972526475787163</v>
+        <v>-0.002972520887851715</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003175375983119011</v>
+        <v>-0.003175344318151474</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003270598128437996</v>
+        <v>-0.003270562738180161</v>
       </c>
       <c r="JB106" t="n">
         <v>0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003397310152649879</v>
+        <v>-0.003397293388843536</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003428259864449501</v>
+        <v>-0.003428224474191666</v>
       </c>
       <c r="JB108" t="n">
         <v>0.1199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003255007788538933</v>
+        <v>-0.003254994750022888</v>
       </c>
       <c r="JB109" t="n">
         <v>0.1199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003130903467535973</v>
+        <v>-0.00313090905547142</v>
       </c>
       <c r="JB110" t="n">
         <v>0.1199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002951560541987419</v>
+        <v>-0.002951513975858688</v>
       </c>
       <c r="JB111" t="n">
         <v>0.2599999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003063878044486046</v>
+        <v>-0.003063835203647614</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.0030862707644701</v>
+        <v>-0.003086287528276443</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002986745908856392</v>
+        <v>-0.002986736595630646</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002954533323645592</v>
+        <v>-0.002954527735710144</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.00298457033932209</v>
+        <v>-0.002984583377838135</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003011947497725487</v>
+        <v>-0.003011997789144516</v>
       </c>
       <c r="JB117" t="n">
         <v>0.1199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003025466576218605</v>
+        <v>-0.003025531768798828</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003193071112036705</v>
+        <v>-0.003193169832229614</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003343066200613976</v>
+        <v>-0.003343131393194199</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003365045413374901</v>
+        <v>-0.003365039825439453</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003324339166283607</v>
+        <v>-0.003324329853057861</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003253372386097908</v>
+        <v>-0.00325331836938858</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003227485343813896</v>
+        <v>-0.003227461129426956</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003183377906680107</v>
+        <v>-0.003183357417583466</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7900000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003130180761218071</v>
+        <v>-0.003130178898572922</v>
       </c>
       <c r="JB126" t="n">
         <v>1</v>
